--- a/Outputs_primates/AllGenes_>49variants_Katie.xlsx
+++ b/Outputs_primates/AllGenes_>49variants_Katie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adesinamary/Documents/GitHub/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270C60BE-2E8A-B847-AB3E-09B64242C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750561F6-0859-0F4C-A2A8-4C0AAAE20345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15520" yWindow="7060" windowWidth="15340" windowHeight="17440" xr2:uid="{F0389E05-49D8-4340-AB03-1574F122DBB0}"/>
   </bookViews>
@@ -3224,15 +3224,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3616,7 +3613,7 @@
     <col min="1" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
